--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{121C1C3A-3BA2-4620-9318-3612089E1262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445BD9BB-FDE9-4C6E-A87E-0CECD522C369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="564" windowWidth="30696" windowHeight="15996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -217,6 +217,10 @@
   </si>
   <si>
     <t>101,2000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissionOne,3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -819,7 +823,9 @@
       <c r="L6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="M6" s="1"/>
+      <c r="M6" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B7">

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445BD9BB-FDE9-4C6E-A87E-0CECD522C369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2904BFB6-A0BD-4049-8C33-75EEB4C6375F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="564" windowWidth="30696" windowHeight="15996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="57">
   <si>
     <t>##var</t>
   </si>
@@ -116,9 +116,6 @@
   </si>
   <si>
     <t>Work</t>
-  </si>
-  <si>
-    <t>22,6</t>
   </si>
   <si>
     <t>gameover</t>
@@ -143,17 +140,55 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>NormalLottery</t>
+  </si>
+  <si>
+    <t>mission:1000</t>
+  </si>
+  <si>
+    <t>MissionOne,2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>gameover</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务奖励（ItemID,num;ItemID,num）</t>
+  </si>
+  <si>
+    <t>healthBelow:95</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissionOne,3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HomePurchase</t>
+  </si>
+  <si>
+    <t>mission:1001</t>
+  </si>
+  <si>
+    <t>101,500</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>MissionOne,4</t>
+  </si>
+  <si>
+    <t>MissionOne,5</t>
+  </si>
+  <si>
+    <t>添置家具</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <t>前往系统空间，使用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>⌈</t>
+      <t>前往系统空间，使用&lt;</t>
     </r>
     <r>
       <rPr>
@@ -163,64 +198,20 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>时间币</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>⌋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>进行一次抽奖</t>
+      <t>时间币&gt;进行一次抽奖</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>NormalLottery</t>
-  </si>
-  <si>
-    <t>mission:1000</t>
-  </si>
-  <si>
-    <t>MissionOne,2</t>
+    <t>购买家具&lt;三人沙发&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>gameover</t>
+    <t>101,500</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>22,6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>任务奖励（ItemID,num;ItemID,num）</t>
-  </si>
-  <si>
-    <t>101,2000;102,1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>healthBelow:95</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>101,2000</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MissionOne,3</t>
+    <t>101,500;102,1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -228,7 +219,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,12 +240,6 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="3"/>
     </font>
     <font>
       <sz val="11"/>
@@ -572,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
@@ -738,7 +723,7 @@
         <v>24</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>25</v>
@@ -774,109 +759,119 @@
         <v>1</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="16.8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="F6" s="1">
         <v>1010</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B7">
+        <v>1002</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7">
+        <v>5002</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B8">
         <v>2000</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7">
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8">
         <v>100</v>
       </c>
-      <c r="J7">
+      <c r="J8">
         <v>6</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B8"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B9"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
+      <c r="K8" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B10"/>
@@ -904,9 +899,9 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12"/>
       <c r="H12"/>
@@ -975,7 +970,16 @@
       <c r="K17"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
       <c r="F18" s="1"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F19" s="1"/>
@@ -988,6 +992,9 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F23" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DE0541-314B-4960-9493-B50F601A43B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3AA7D3-6771-487E-B266-3A5AD13CFFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -112,6 +112,30 @@
     <t>任务结束时对话</t>
   </si>
   <si>
+    <t>第一桶金</t>
+  </si>
+  <si>
+    <t>在25岁前积累5000模拟币</t>
+  </si>
+  <si>
+    <t>SimulationCoinBalance</t>
+  </si>
+  <si>
+    <t>mission:1003</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>25,1</t>
+  </si>
+  <si>
+    <t>gameover</t>
+  </si>
+  <si>
+    <t>外出捕食</t>
+  </si>
+  <si>
     <t>完成一次零工</t>
   </si>
   <si>
@@ -121,9 +145,6 @@
     <t>101,500</t>
   </si>
   <si>
-    <t>gameover</t>
-  </si>
-  <si>
     <t>MissionOne,0</t>
   </si>
   <si>
@@ -169,6 +190,21 @@
     <t>MissionOne,5</t>
   </si>
   <si>
+    <t>温馨小屋</t>
+  </si>
+  <si>
+    <t>查看小屋满意度面板</t>
+  </si>
+  <si>
+    <t>HomeSatisfactionView</t>
+  </si>
+  <si>
+    <t>mission:1002</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>生病啦</t>
   </si>
   <si>
@@ -181,42 +217,20 @@
     <t>healthBelow:95</t>
   </si>
   <si>
-    <t>温馨小屋</t>
-  </si>
-  <si>
-    <t>查看小屋满意度面板</t>
-  </si>
-  <si>
-    <t>HomeSatisfactionView</t>
-  </si>
-  <si>
-    <t>mission:1002</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>SimulationCoinBalance</t>
-  </si>
-  <si>
-    <t>mission:1003</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>25,1</t>
-  </si>
-  <si>
-    <t>外出捕食</t>
+    <t>MysteryWheelLottery</t>
+  </si>
+  <si>
+    <t>wheelCoinObtained</t>
+  </si>
+  <si>
+    <t>MissionThree,0</t>
+  </si>
+  <si>
+    <t>神秘转盘！</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>第一桶金</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>在25岁前积累5000模拟币</t>
+    <t>获得了一枚&lt;转盘币&gt;，使用其进行一次抽奖</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -741,29 +755,29 @@
         <v>100</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>3000</v>
       </c>
       <c r="G5" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="H5" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L5"/>
       <c r="M5"/>
@@ -773,13 +787,13 @@
         <v>1000</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F6" s="1">
         <v>1000</v>
@@ -789,17 +803,17 @@
         <v>1</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -807,35 +821,35 @@
         <v>1001</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F7" s="1">
         <v>1010</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -843,35 +857,35 @@
         <v>1002</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F8">
         <v>5002</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -879,29 +893,29 @@
         <v>1003</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J9"/>
       <c r="K9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L9"/>
       <c r="M9"/>
@@ -911,17 +925,17 @@
         <v>2000</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="H10">
         <v>100</v>
@@ -930,7 +944,35 @@
         <v>6</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>3000</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1011</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" t="s">
+        <v>60</v>
+      </c>
+      <c r="J11"/>
+      <c r="K11" s="1"/>
+      <c r="L11" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3AA7D3-6771-487E-B266-3A5AD13CFFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22E3E7C-18E0-4E66-9B7A-4EB3E651CB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -214,9 +214,6 @@
     <t>Health</t>
   </si>
   <si>
-    <t>healthBelow:95</t>
-  </si>
-  <si>
     <t>MysteryWheelLottery</t>
   </si>
   <si>
@@ -231,6 +228,10 @@
   </si>
   <si>
     <t>获得了一枚&lt;转盘币&gt;，使用其进行一次抽奖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>healthBelow:40</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -257,6 +258,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -570,23 +572,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="16" style="2" customWidth="1"/>
     <col min="4" max="4" width="35" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="25.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="23.375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="18.375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="20.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="25.44140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="20.21875" style="2" customWidth="1"/>
     <col min="13" max="13" width="20" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -627,7 +629,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -668,7 +670,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -709,7 +711,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -750,7 +752,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>100</v>
       </c>
@@ -782,7 +784,7 @@
       <c r="L5"/>
       <c r="M5"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1000</v>
       </c>
@@ -816,7 +818,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1001</v>
       </c>
@@ -852,7 +854,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1002</v>
       </c>
@@ -888,7 +890,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1003</v>
       </c>
@@ -920,7 +922,7 @@
       <c r="L9"/>
       <c r="M9"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>2000</v>
       </c>
@@ -935,10 +937,10 @@
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -947,24 +949,24 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>3000</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F11" s="1">
         <v>1011</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H11" t="s">
         <v>60</v>
@@ -972,10 +974,10 @@
       <c r="J11"/>
       <c r="K11" s="1"/>
       <c r="L11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B13"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -987,7 +989,7 @@
       <c r="J13"/>
       <c r="K13"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -999,7 +1001,7 @@
       <c r="J14"/>
       <c r="K14"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
@@ -1011,7 +1013,7 @@
       <c r="J15"/>
       <c r="K15"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1023,7 +1025,7 @@
       <c r="J16"/>
       <c r="K16"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -1035,7 +1037,7 @@
       <c r="J17"/>
       <c r="K17"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -1047,7 +1049,7 @@
       <c r="J18"/>
       <c r="K18"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -1059,7 +1061,7 @@
       <c r="J19"/>
       <c r="K19"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -1071,19 +1073,19 @@
       <c r="J20"/>
       <c r="K20"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F25" s="1"/>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22E3E7C-18E0-4E66-9B7A-4EB3E651CB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324809E9-C604-4E50-B08F-011D995E635B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -46,6 +46,9 @@
     <t>target</t>
   </si>
   <si>
+    <t>randomTarget</t>
+  </si>
+  <si>
     <t>reward</t>
   </si>
   <si>
@@ -97,6 +100,9 @@
     <t>任务目标</t>
   </si>
   <si>
+    <t>任务目标随机池</t>
+  </si>
+  <si>
     <t>任务奖励（ItemID,num;ItemID,num）</t>
   </si>
   <si>
@@ -121,9 +127,6 @@
     <t>SimulationCoinBalance</t>
   </si>
   <si>
-    <t>mission:1003</t>
-  </si>
-  <si>
     <t>5000</t>
   </si>
   <si>
@@ -214,6 +217,15 @@
     <t>Health</t>
   </si>
   <si>
+    <t>healthBelow:40</t>
+  </si>
+  <si>
+    <t>神秘转盘！</t>
+  </si>
+  <si>
+    <t>获得了一枚&lt;转盘币&gt;，使用其进行一次抽奖</t>
+  </si>
+  <si>
     <t>MysteryWheelLottery</t>
   </si>
   <si>
@@ -223,15 +235,22 @@
     <t>MissionThree,0</t>
   </si>
   <si>
-    <t>神秘转盘！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得了一枚&lt;转盘币&gt;，使用其进行一次抽奖</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>healthBelow:40</t>
+    <t>特殊事件</t>
+  </si>
+  <si>
+    <t>你触发了特殊事件，快去收集&lt;{0}&gt;*{1}吧</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>4000,1,50;4001,1,30;4003,1,20</t>
+  </si>
+  <si>
+    <t>3001,3;101,300</t>
+  </si>
+  <si>
+    <t>mission:1003;force:22,2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -258,7 +277,6 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -571,24 +589,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="16" style="2" customWidth="1"/>
     <col min="4" max="4" width="35" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="25.44140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="23.33203125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="20.21875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="20" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="23.375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="20.25" style="2" customWidth="1"/>
+    <col min="14" max="14" width="20" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -613,7 +632,7 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -628,174 +647,186 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>100</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F5">
         <v>3000</v>
       </c>
-      <c r="G5" t="s">
-        <v>33</v>
+      <c r="G5" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5"/>
-      <c r="J5" t="s">
         <v>35</v>
       </c>
+      <c r="J5"/>
       <c r="K5" t="s">
         <v>36</v>
       </c>
-      <c r="L5"/>
+      <c r="L5" t="s">
+        <v>37</v>
+      </c>
       <c r="M5"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1000</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" s="1">
         <v>1000</v>
@@ -804,180 +835,206 @@
       <c r="H6">
         <v>1</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="J6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="1"/>
       <c r="L6" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1001</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" s="1">
         <v>1010</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="J7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>1002</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F8">
         <v>5002</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="J8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N8" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>1003</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9"/>
-      <c r="K9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L9"/>
+        <v>61</v>
+      </c>
+      <c r="J9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9"/>
+      <c r="L9" t="s">
+        <v>37</v>
+      </c>
       <c r="M9"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N9"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>2000</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H10">
         <v>80</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>6</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L10" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>3000</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="F11" s="1">
         <v>1011</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
-      </c>
-      <c r="J11"/>
-      <c r="K11" s="1"/>
-      <c r="L11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="K11"/>
+      <c r="L11" s="1"/>
+      <c r="M11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>3001</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12">
+        <v>3001</v>
+      </c>
+      <c r="I12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B13"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -985,11 +1042,11 @@
       <c r="F13" s="1"/>
       <c r="G13"/>
       <c r="H13"/>
-      <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L13"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B14"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -997,11 +1054,11 @@
       <c r="F14" s="1"/>
       <c r="G14"/>
       <c r="H14"/>
-      <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L14"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
@@ -1009,11 +1066,11 @@
       <c r="F15" s="1"/>
       <c r="G15"/>
       <c r="H15"/>
-      <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L15"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1021,11 +1078,11 @@
       <c r="F16" s="1"/>
       <c r="G16"/>
       <c r="H16"/>
-      <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L16"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -1033,11 +1090,11 @@
       <c r="F17" s="1"/>
       <c r="G17"/>
       <c r="H17"/>
-      <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L17"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -1045,11 +1102,11 @@
       <c r="F18" s="1"/>
       <c r="G18"/>
       <c r="H18"/>
-      <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L18"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -1057,11 +1114,11 @@
       <c r="F19" s="1"/>
       <c r="G19"/>
       <c r="H19"/>
-      <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L19"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -1069,23 +1126,23 @@
       <c r="F20" s="1"/>
       <c r="G20"/>
       <c r="H20"/>
-      <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L20"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="F25" s="1"/>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324809E9-C604-4E50-B08F-011D995E635B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C85460-8380-4237-A2D6-DBD0E8BEFAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -127,6 +127,9 @@
     <t>SimulationCoinBalance</t>
   </si>
   <si>
+    <t>mission:1003;force:22,2</t>
+  </si>
+  <si>
     <t>5000</t>
   </si>
   <si>
@@ -157,9 +160,6 @@
     <t>从天而降的好运</t>
   </si>
   <si>
-    <t>前往系统空间，使用&lt;时间币&gt;进行一次抽奖</t>
-  </si>
-  <si>
     <t>NormalLottery</t>
   </si>
   <si>
@@ -178,10 +178,10 @@
     <t>添置家具</t>
   </si>
   <si>
-    <t>购买家具&lt;三人沙发&gt;</t>
-  </si>
-  <si>
-    <t>HomePurchase</t>
+    <t>购买任意家具</t>
+  </si>
+  <si>
+    <t>HomePurchaseAny</t>
   </si>
   <si>
     <t>mission:1001</t>
@@ -223,9 +223,6 @@
     <t>神秘转盘！</t>
   </si>
   <si>
-    <t>获得了一枚&lt;转盘币&gt;，使用其进行一次抽奖</t>
-  </si>
-  <si>
     <t>MysteryWheelLottery</t>
   </si>
   <si>
@@ -238,19 +235,24 @@
     <t>特殊事件</t>
   </si>
   <si>
-    <t>你触发了特殊事件，快去收集&lt;{0}&gt;*{1}吧</t>
+    <t>社区发布公告，需要收集&lt;{0}&gt;*{1}</t>
+  </si>
+  <si>
+    <t>5000,3,10;5001,3,10;5002,3,10;5003,3,10;5004,3,10;5005,3,10</t>
+  </si>
+  <si>
+    <t>3011,1</t>
+  </si>
+  <si>
+    <t>获得了一枚&lt;color=blue&gt;转盘币&lt;/color&gt;，使用其进行一次抽奖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Item</t>
-  </si>
-  <si>
-    <t>4000,1,50;4001,1,30;4003,1,20</t>
-  </si>
-  <si>
-    <t>3001,3;101,300</t>
-  </si>
-  <si>
-    <t>mission:1003;force:22,2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>前往系统空间，使用&lt;color=#00FFFA&gt;时间币&lt;/color&gt;进行一次抽奖</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -277,6 +279,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -797,20 +800,20 @@
         <v>34</v>
       </c>
       <c r="F5">
-        <v>3000</v>
+        <v>1002</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J5"/>
       <c r="K5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M5"/>
       <c r="N5"/>
@@ -820,33 +823,31 @@
         <v>1000</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" s="1">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K6" s="1"/>
-      <c r="L6" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -854,10 +855,10 @@
         <v>1001</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>46</v>
@@ -875,9 +876,7 @@
         <v>48</v>
       </c>
       <c r="K7" s="1"/>
-      <c r="L7" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
         <v>49</v>
       </c>
@@ -899,7 +898,7 @@
         <v>53</v>
       </c>
       <c r="F8">
-        <v>5002</v>
+        <v>2000</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>54</v>
@@ -908,12 +907,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K8" s="1"/>
-      <c r="L8" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
         <v>55</v>
       </c>
@@ -935,7 +932,7 @@
         <v>59</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G9" t="s">
         <v>60</v>
@@ -944,12 +941,10 @@
         <v>61</v>
       </c>
       <c r="J9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K9"/>
-      <c r="L9" t="s">
-        <v>37</v>
-      </c>
+      <c r="L9"/>
       <c r="M9"/>
       <c r="N9"/>
     </row>
@@ -966,7 +961,9 @@
       <c r="E10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="1"/>
+      <c r="F10" s="1">
+        <v>1050</v>
+      </c>
       <c r="G10" s="1" t="s">
         <v>65</v>
       </c>
@@ -977,7 +974,7 @@
         <v>6</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -988,16 +985,16 @@
         <v>66</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="F11" s="1">
         <v>1011</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H11" t="s">
         <v>61</v>
@@ -1005,7 +1002,7 @@
       <c r="K11"/>
       <c r="L11" s="1"/>
       <c r="M11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -1013,22 +1010,22 @@
         <v>3001</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12">
+        <v>3011</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E12" t="s">
+      <c r="J12" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="F12">
-        <v>3001</v>
-      </c>
-      <c r="I12" t="s">
-        <v>74</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="K12">
         <v>1</v>

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12781AA8-726A-431B-BB2C-5A7E0129D487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7606BE0-EB05-4BD6-B087-D684BA8B96C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-8592" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="100">
   <si>
     <t>##var</t>
   </si>
@@ -281,9 +281,6 @@
   </si>
   <si>
     <t>海洋之心</t>
-  </si>
-  <si>
-    <t>收集&lt;color=#00FFFA&gt;{0}&lt;/color&gt;×{1}</t>
   </si>
   <si>
     <t>satisfactionAtLeast:40</t>
@@ -312,6 +309,22 @@
   </si>
   <si>
     <t>MissionThree,2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissionThree,3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissionThree,4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>收集&lt;color=#00FFFA&gt;{0}&lt;/color&gt;×{1}，送给喵夫人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>女儿的心愿，收集&lt;color=#00FFFA&gt;{0}&lt;/color&gt;×{1}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -652,25 +665,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="16" style="2" customWidth="1"/>
-    <col min="4" max="4" width="60.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="23.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="20.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="60.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.21875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.44140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="23.33203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="20.21875" style="2" customWidth="1"/>
     <col min="14" max="14" width="20" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.625" customWidth="1"/>
+    <col min="15" max="15" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -717,7 +730,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -764,7 +777,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -811,7 +824,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -858,7 +871,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>100</v>
       </c>
@@ -891,7 +904,7 @@
       </c>
       <c r="N5"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>101</v>
       </c>
@@ -924,7 +937,7 @@
       </c>
       <c r="N6"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1000</v>
       </c>
@@ -956,7 +969,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1001</v>
       </c>
@@ -990,7 +1003,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1002</v>
       </c>
@@ -1024,7 +1037,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1003</v>
       </c>
@@ -1053,7 +1066,7 @@
       <c r="M10"/>
       <c r="N10"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>2000</v>
       </c>
@@ -1082,7 +1095,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>3000</v>
       </c>
@@ -1110,7 +1123,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>3001</v>
       </c>
@@ -1139,7 +1152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>3002</v>
       </c>
@@ -1147,7 +1160,7 @@
         <v>86</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>82</v>
@@ -1156,29 +1169,35 @@
         <v>5101</v>
       </c>
       <c r="G14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" t="s">
         <v>88</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>89</v>
       </c>
-      <c r="I14" t="s">
+      <c r="K14" t="s">
         <v>90</v>
-      </c>
-      <c r="K14" t="s">
-        <v>91</v>
       </c>
       <c r="L14"/>
       <c r="M14"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>3003</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>82</v>
@@ -1187,27 +1206,27 @@
         <v>5100</v>
       </c>
       <c r="G15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" t="s">
         <v>93</v>
       </c>
-      <c r="H15" t="s">
-        <v>94</v>
-      </c>
       <c r="I15" t="s">
+        <v>89</v>
+      </c>
+      <c r="K15" t="s">
         <v>90</v>
-      </c>
-      <c r="K15" t="s">
-        <v>91</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O15" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="O15" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1219,7 +1238,7 @@
       <c r="L16"/>
       <c r="M16"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -1231,7 +1250,7 @@
       <c r="L17"/>
       <c r="M17"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -1243,7 +1262,7 @@
       <c r="L18"/>
       <c r="M18"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -1255,7 +1274,7 @@
       <c r="L19"/>
       <c r="M19"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -1267,7 +1286,7 @@
       <c r="L20"/>
       <c r="M20"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1279,19 +1298,19 @@
       <c r="L21"/>
       <c r="M21"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F26" s="1"/>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7606BE0-EB05-4BD6-B087-D684BA8B96C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2617152-8CF5-4201-823E-1065516821B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-8592" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,9 +184,6 @@
     <t>从天而降的好运</t>
   </si>
   <si>
-    <t>前往系统空间，使用&lt;color=#00FFFA&gt;时间币&lt;/color&gt;进行一次抽奖</t>
-  </si>
-  <si>
     <t>NormalLottery</t>
   </si>
   <si>
@@ -260,9 +257,6 @@
   </si>
   <si>
     <t>MissionThree,0</t>
-  </si>
-  <si>
-    <t>特殊事件</t>
   </si>
   <si>
     <t>社区发布公告，需要提交&lt;color=#00FFFA&gt;{0}&lt;/color&gt;*{1}</t>
@@ -325,6 +319,14 @@
   </si>
   <si>
     <t>女儿的心愿，收集&lt;color=#00FFFA&gt;{0}&lt;/color&gt;×{1}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>前往系统空间，使用&lt;color=#00FFFA&gt;时间币&lt;/color&gt;进行一次抽奖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>社区物资需求</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -351,6 +353,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -977,30 +980,30 @@
         <v>53</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="F8" s="1">
         <v>1010</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -1008,19 +1011,19 @@
         <v>1002</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="F9">
         <v>2000</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1031,10 +1034,10 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1042,22 +1045,22 @@
         <v>1003</v>
       </c>
       <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" t="s">
         <v>66</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>67</v>
-      </c>
-      <c r="E10" t="s">
-        <v>68</v>
       </c>
       <c r="F10">
         <v>2000</v>
       </c>
       <c r="G10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" t="s">
         <v>69</v>
-      </c>
-      <c r="H10" t="s">
-        <v>70</v>
       </c>
       <c r="K10" t="s">
         <v>50</v>
@@ -1071,19 +1074,19 @@
         <v>2000</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="F11" s="1">
         <v>1050</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H11">
         <v>80</v>
@@ -1100,27 +1103,27 @@
         <v>3000</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="F12" s="1">
         <v>1011</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L12"/>
       <c r="M12" s="1"/>
       <c r="N12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1128,25 +1131,25 @@
         <v>3001</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="F13">
         <v>3011</v>
       </c>
       <c r="I13" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -1157,36 +1160,36 @@
         <v>3002</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F14" s="1">
         <v>5101</v>
       </c>
       <c r="G14" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" t="s">
+        <v>86</v>
+      </c>
+      <c r="I14" t="s">
         <v>87</v>
       </c>
-      <c r="H14" t="s">
+      <c r="K14" t="s">
         <v>88</v>
-      </c>
-      <c r="I14" t="s">
-        <v>89</v>
-      </c>
-      <c r="K14" t="s">
-        <v>90</v>
       </c>
       <c r="L14"/>
       <c r="M14"/>
       <c r="N14" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -1194,36 +1197,36 @@
         <v>3003</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F15" s="1">
         <v>5100</v>
       </c>
       <c r="G15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2617152-8CF5-4201-823E-1065516821B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42918732-3D88-4C7D-BDDB-F65A82618253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-8592" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="106">
   <si>
     <t>##var</t>
   </si>
@@ -184,6 +184,9 @@
     <t>从天而降的好运</t>
   </si>
   <si>
+    <t>前往系统空间，使用&lt;color=#00FFFA&gt;时间币&lt;/color&gt;进行一次抽奖</t>
+  </si>
+  <si>
     <t>NormalLottery</t>
   </si>
   <si>
@@ -259,7 +262,10 @@
     <t>MissionThree,0</t>
   </si>
   <si>
-    <t>社区发布公告，需要提交&lt;color=#00FFFA&gt;{0}&lt;/color&gt;*{1}</t>
+    <t>社区物资需求</t>
+  </si>
+  <si>
+    <t>社区发布需求，需要提交&lt;color=#00FFFA&gt;{0}&lt;/color&gt;*{1}</t>
   </si>
   <si>
     <t>Item</t>
@@ -277,6 +283,9 @@
     <t>海洋之心</t>
   </si>
   <si>
+    <t>收集&lt;color=#00FFFA&gt;{0}&lt;/color&gt;×{1}，送给喵夫人</t>
+  </si>
+  <si>
     <t>satisfactionAtLeast:40</t>
   </si>
   <si>
@@ -289,9 +298,18 @@
     <t>3001,1;4023,3</t>
   </si>
   <si>
+    <t>MissionThree,3</t>
+  </si>
+  <si>
+    <t>MissionThree,4</t>
+  </si>
+  <si>
     <t>草莓小熊</t>
   </si>
   <si>
+    <t>女儿的心愿，收集&lt;color=#00FFFA&gt;{0}&lt;/color&gt;×{1}</t>
+  </si>
+  <si>
     <t>unlockedHomeIdRangeCount:7000,7999,3</t>
   </si>
   <si>
@@ -299,34 +317,27 @@
   </si>
   <si>
     <t>MissionThree,1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>MissionThree,2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MissionThree,3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MissionThree,4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>收集&lt;color=#00FFFA&gt;{0}&lt;/color&gt;×{1}，送给喵夫人</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>女儿的心愿，收集&lt;color=#00FFFA&gt;{0}&lt;/color&gt;×{1}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>前往系统空间，使用&lt;color=#00FFFA&gt;时间币&lt;/color&gt;进行一次抽奖</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>社区物资需求</t>
+  </si>
+  <si>
+    <t>社区鱼获需求</t>
+  </si>
+  <si>
+    <t>FishCatch</t>
+  </si>
+  <si>
+    <t>mission:3003</t>
+  </si>
+  <si>
+    <t>6000,3;6001,3;6002,3;6003,2;6004,2;6005,2;6006,1;6007,1;6008,1;6009,1;6010,1</t>
+  </si>
+  <si>
+    <t>6000,3,10;6001,3,10;6002,3,10;6003,2,10;6004,2,10;6005,2,10;6006,1,10;6007,1,10;6008,1,10;6009,1,10;6010,1,10</t>
+  </si>
+  <si>
+    <t>请亲自钓起以下鱼获，已有鱼获不计：{0}*{1}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -668,25 +679,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="16" style="2" customWidth="1"/>
-    <col min="4" max="4" width="60.21875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="23.21875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.44140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.33203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="60.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="23.375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="20.25" style="2" customWidth="1"/>
     <col min="14" max="14" width="20" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.6640625" customWidth="1"/>
+    <col min="15" max="15" width="24.625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -733,7 +744,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -780,7 +791,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -827,7 +838,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -874,7 +885,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>100</v>
       </c>
@@ -907,7 +918,7 @@
       </c>
       <c r="N5"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>101</v>
       </c>
@@ -940,7 +951,7 @@
       </c>
       <c r="N6"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1000</v>
       </c>
@@ -972,7 +983,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>1001</v>
       </c>
@@ -980,50 +991,50 @@
         <v>53</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F8" s="1">
         <v>1010</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>1002</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F9">
         <v>2000</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1034,33 +1045,33 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>1003</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F10">
         <v>2000</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K10" t="s">
         <v>50</v>
@@ -1069,24 +1080,24 @@
       <c r="M10"/>
       <c r="N10"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>2000</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F11" s="1">
         <v>1050</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H11">
         <v>80</v>
@@ -1098,150 +1109,171 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>3000</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F12" s="1">
         <v>1011</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L12"/>
       <c r="M12" s="1"/>
       <c r="N12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>3001</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F13">
         <v>3011</v>
       </c>
       <c r="I13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>3002</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" s="1">
         <v>5101</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L14"/>
       <c r="M14"/>
       <c r="N14" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>3003</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F15" s="1">
         <v>5100</v>
       </c>
       <c r="G15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" t="s">
         <v>90</v>
       </c>
-      <c r="H15" t="s">
+      <c r="K15" t="s">
         <v>91</v>
-      </c>
-      <c r="I15" t="s">
-        <v>87</v>
-      </c>
-      <c r="K15" t="s">
-        <v>88</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16" s="1"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="K16"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>3004</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16">
+        <v>6000</v>
+      </c>
+      <c r="G16" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16" t="s">
+        <v>90</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="L16"/>
-      <c r="M16"/>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -1253,7 +1285,7 @@
       <c r="L17"/>
       <c r="M17"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -1265,7 +1297,7 @@
       <c r="L18"/>
       <c r="M18"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -1277,7 +1309,7 @@
       <c r="L19"/>
       <c r="M19"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -1289,7 +1321,7 @@
       <c r="L20"/>
       <c r="M20"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1301,19 +1333,19 @@
       <c r="L21"/>
       <c r="M21"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
       <c r="F26" s="1"/>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42918732-3D88-4C7D-BDDB-F65A82618253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4645E3B7-D7EA-4CF2-83C8-D6E7F06E1505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -127,9 +127,6 @@
     <t>第一桶金</t>
   </si>
   <si>
-    <t>在25岁前积累5000模拟币，然后去看看外边的世界吧</t>
-  </si>
-  <si>
     <t>SimulationCoinBalance</t>
   </si>
   <si>
@@ -142,27 +139,18 @@
     <t>4028,1</t>
   </si>
   <si>
-    <t>25,1</t>
-  </si>
-  <si>
     <t>gameover</t>
   </si>
   <si>
     <t>风起</t>
   </si>
   <si>
-    <t>生活压力变大了，在28岁前攒到20000模拟币</t>
-  </si>
-  <si>
     <t>mission:100</t>
   </si>
   <si>
     <t>1012,1</t>
   </si>
   <si>
-    <t>28,1</t>
-  </si>
-  <si>
     <t>外出捕食</t>
   </si>
   <si>
@@ -338,6 +326,22 @@
   </si>
   <si>
     <t>请亲自钓起以下鱼获，已有鱼获不计：{0}*{1}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在24岁前积累5000模拟币，然后去看看外边的世界吧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生活压力变大了，在26岁前攒到20000模拟币</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>24,1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26,1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -679,25 +683,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="16" style="2" customWidth="1"/>
-    <col min="4" max="4" width="60.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="23.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="20.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="60.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.21875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.44140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="23.33203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="20.21875" style="2" customWidth="1"/>
     <col min="14" max="14" width="20" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="24.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -744,7 +748,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -791,7 +795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -838,7 +842,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -885,7 +889,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>100</v>
       </c>
@@ -893,76 +897,76 @@
         <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" t="s">
         <v>35</v>
-      </c>
-      <c r="E5" t="s">
-        <v>36</v>
       </c>
       <c r="F5">
         <v>1002</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
         <v>37</v>
       </c>
-      <c r="H5" t="s">
+      <c r="K5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M5" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" t="s">
-        <v>41</v>
-      </c>
       <c r="N5"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>101</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6">
         <v>1002</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H6">
         <v>20000</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N6"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1000</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F7" s="1">
         <v>4000</v>
@@ -972,132 +976,132 @@
         <v>1</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1001</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F8" s="1">
         <v>1010</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1002</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F9">
         <v>2000</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1003</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F10">
         <v>2000</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L10"/>
       <c r="M10"/>
       <c r="N10"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>2000</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F11" s="1">
         <v>1050</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H11">
         <v>80</v>
@@ -1106,174 +1110,174 @@
         <v>6</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>3000</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F12" s="1">
         <v>1011</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="L12"/>
       <c r="M12" s="1"/>
       <c r="N12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>3001</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F13">
         <v>3011</v>
       </c>
       <c r="I13" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>3002</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F14" s="1">
         <v>5101</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I14" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L14"/>
       <c r="M14"/>
       <c r="N14" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>3003</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F15" s="1">
         <v>5100</v>
       </c>
       <c r="G15" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H15" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>3004</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F16">
         <v>6000</v>
       </c>
       <c r="G16" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H16" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I16" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L16"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -1285,7 +1289,7 @@
       <c r="L17"/>
       <c r="M17"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -1297,7 +1301,7 @@
       <c r="L18"/>
       <c r="M18"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -1309,7 +1313,7 @@
       <c r="L19"/>
       <c r="M19"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -1321,7 +1325,7 @@
       <c r="L20"/>
       <c r="M20"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1333,19 +1337,19 @@
       <c r="L21"/>
       <c r="M21"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F26" s="1"/>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4645E3B7-D7EA-4CF2-83C8-D6E7F06E1505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCECE5B-E4DE-4DE1-A476-A1B90B1774AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="564" windowWidth="30696" windowHeight="15996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="111">
   <si>
     <t>##var</t>
   </si>
@@ -151,19 +151,10 @@
     <t>1012,1</t>
   </si>
   <si>
-    <t>外出捕食</t>
-  </si>
-  <si>
     <t>完成一次零工</t>
   </si>
   <si>
-    <t>Work</t>
-  </si>
-  <si>
     <t>101,500</t>
-  </si>
-  <si>
-    <t>MissionOne,0</t>
   </si>
   <si>
     <t>MissionOne,1</t>
@@ -342,6 +333,36 @@
   </si>
   <si>
     <t>26,1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>熊大山工具带得很齐，却唯独忘记了最普通的强力胶带</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>熊大山</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5102,1</t>
+  </si>
+  <si>
+    <t>MissionRole,0</t>
+  </si>
+  <si>
+    <t>外出捕食</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissionOne,0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Work</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>force:22,6</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -682,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
@@ -897,7 +918,7 @@
         <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
         <v>35</v>
@@ -915,7 +936,7 @@
         <v>38</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s">
         <v>39</v>
@@ -930,7 +951,7 @@
         <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
         <v>35</v>
@@ -948,7 +969,7 @@
         <v>42</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>39</v>
@@ -957,337 +978,357 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B7">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>46</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7">
+        <v>5012</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-      <c r="N7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>48</v>
+      <c r="N7" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B8">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="F8" s="1">
-        <v>1010</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>4000</v>
+      </c>
+      <c r="G8" s="1"/>
       <c r="H8">
         <v>1</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>53</v>
+      <c r="K8" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B9">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9">
-        <v>2000</v>
+        <v>48</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1010</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B10">
-        <v>1003</v>
-      </c>
-      <c r="C10" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" t="s">
-        <v>64</v>
+        <v>1002</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="F10">
         <v>2000</v>
       </c>
-      <c r="G10" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10"/>
-      <c r="M10"/>
-      <c r="N10"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11">
+        <v>1003</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11">
         <v>2000</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1050</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H11">
-        <v>80</v>
-      </c>
-      <c r="L11">
-        <v>6</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="G11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B12">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F12" s="1">
-        <v>1011</v>
+        <v>1050</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" t="s">
-        <v>66</v>
-      </c>
-      <c r="L12"/>
-      <c r="M12" s="1"/>
-      <c r="N12" t="s">
-        <v>75</v>
+        <v>67</v>
+      </c>
+      <c r="H12">
+        <v>80</v>
+      </c>
+      <c r="L12">
+        <v>6</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B13">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F13">
-        <v>3011</v>
-      </c>
-      <c r="I13" t="s">
-        <v>79</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
+        <v>70</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1011</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" t="s">
+        <v>63</v>
+      </c>
+      <c r="L13"/>
+      <c r="M13" s="1"/>
+      <c r="N13" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B14">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14">
+        <v>3011</v>
+      </c>
+      <c r="I14" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F14" s="1">
-        <v>5101</v>
-      </c>
-      <c r="G14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H14" t="s">
-        <v>85</v>
-      </c>
-      <c r="I14" t="s">
-        <v>86</v>
-      </c>
-      <c r="K14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L14"/>
-      <c r="M14"/>
-      <c r="N14" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>89</v>
+      <c r="L14">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B15">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F15" s="1">
-        <v>5100</v>
+        <v>5101</v>
       </c>
       <c r="G15" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K15" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15" s="4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B16">
+        <v>3003</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="1">
+        <v>5100</v>
+      </c>
+      <c r="G16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B17">
         <v>3004</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17">
+        <v>6000</v>
+      </c>
+      <c r="G17" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="I17" t="s">
+        <v>83</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F16">
-        <v>6000</v>
-      </c>
-      <c r="G16" t="s">
-        <v>98</v>
-      </c>
-      <c r="H16" t="s">
-        <v>99</v>
-      </c>
-      <c r="I16" t="s">
-        <v>86</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L16"/>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B17"/>
-      <c r="C17"/>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17" s="1"/>
-      <c r="G17"/>
-      <c r="H17"/>
-      <c r="K17"/>
+      <c r="K17" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="L17"/>
-      <c r="M17"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18"/>
@@ -1338,7 +1379,16 @@
       <c r="M21"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
       <c r="F22" s="1"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F23" s="1"/>
@@ -1351,6 +1401,9 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="F27" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCECE5B-E4DE-4DE1-A476-A1B90B1774AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE0A237-AD04-400F-87A2-30B4CCAA1ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="564" windowWidth="30696" windowHeight="15996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -340,10 +340,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>熊大山</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>5102,1</t>
   </si>
   <si>
@@ -363,6 +359,10 @@
   </si>
   <si>
     <t>force:22,6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>代购</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -704,25 +704,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="16" style="2" customWidth="1"/>
-    <col min="4" max="4" width="60.21875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="23.21875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.44140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.33203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="60.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="23.375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="20.25" style="2" customWidth="1"/>
     <col min="14" max="14" width="20" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.6640625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="24.625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -769,7 +769,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -816,7 +816,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -863,7 +863,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -910,7 +910,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>100</v>
       </c>
@@ -943,7 +943,7 @@
       </c>
       <c r="N5"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>101</v>
       </c>
@@ -976,12 +976,12 @@
       </c>
       <c r="N6"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>200</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>103</v>
@@ -993,10 +993,10 @@
         <v>5012</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>83</v>
@@ -1005,21 +1005,21 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>1000</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F8" s="1">
         <v>4000</v>
@@ -1034,13 +1034,13 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>1001</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>1002</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>1003</v>
       </c>
@@ -1137,7 +1137,7 @@
       <c r="M11"/>
       <c r="N11"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>2000</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>3000</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>3001</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>3002</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>3003</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>3004</v>
       </c>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="L17"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -1342,7 +1342,7 @@
       <c r="L18"/>
       <c r="M18"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -1354,7 +1354,7 @@
       <c r="L19"/>
       <c r="M19"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -1366,7 +1366,7 @@
       <c r="L20"/>
       <c r="M20"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1378,7 +1378,7 @@
       <c r="L21"/>
       <c r="M21"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -1390,19 +1390,19 @@
       <c r="L22"/>
       <c r="M22"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
       <c r="F27" s="1"/>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -358,7 +358,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>force:22,6</t>
+    <t>force:22,4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE0A237-AD04-400F-87A2-30B4CCAA1ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44800863-1C47-4FCF-BEE7-420A04939F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="112">
   <si>
     <t>##var</t>
   </si>
@@ -363,6 +363,10 @@
   </si>
   <si>
     <t>代购</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissionRole,1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -416,7 +420,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -428,6 +432,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -704,25 +711,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="16" style="2" customWidth="1"/>
-    <col min="4" max="4" width="60.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="23.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="20.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="60.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.21875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.44140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="23.33203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="20.21875" style="2" customWidth="1"/>
     <col min="14" max="14" width="20" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="24.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -769,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -816,7 +823,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -863,7 +870,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -910,7 +917,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>100</v>
       </c>
@@ -943,7 +950,7 @@
       </c>
       <c r="N5"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>101</v>
       </c>
@@ -976,7 +983,7 @@
       </c>
       <c r="N6"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>200</v>
       </c>
@@ -1007,8 +1014,11 @@
       <c r="N7" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1000</v>
       </c>
@@ -1040,7 +1050,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1001</v>
       </c>
@@ -1074,7 +1084,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1002</v>
       </c>
@@ -1108,7 +1118,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1003</v>
       </c>
@@ -1137,7 +1147,7 @@
       <c r="M11"/>
       <c r="N11"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>2000</v>
       </c>
@@ -1166,7 +1176,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>3000</v>
       </c>
@@ -1194,7 +1204,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>3001</v>
       </c>
@@ -1223,7 +1233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>3002</v>
       </c>
@@ -1260,7 +1270,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>3003</v>
       </c>
@@ -1297,7 +1307,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>3004</v>
       </c>
@@ -1330,7 +1340,7 @@
       </c>
       <c r="L17"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -1342,7 +1352,7 @@
       <c r="L18"/>
       <c r="M18"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -1354,7 +1364,7 @@
       <c r="L19"/>
       <c r="M19"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -1366,7 +1376,7 @@
       <c r="L20"/>
       <c r="M20"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1378,7 +1388,7 @@
       <c r="L21"/>
       <c r="M21"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -1390,19 +1400,19 @@
       <c r="L22"/>
       <c r="M22"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F27" s="1"/>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44800863-1C47-4FCF-BEE7-420A04939F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1448F42-C354-459B-9A03-E352A56941ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="126">
   <si>
     <t>##var</t>
   </si>
@@ -127,6 +127,9 @@
     <t>第一桶金</t>
   </si>
   <si>
+    <t>在24岁前积累5000模拟币，然后去看看外边的世界吧</t>
+  </si>
+  <si>
     <t>SimulationCoinBalance</t>
   </si>
   <si>
@@ -139,24 +142,111 @@
     <t>4028,1</t>
   </si>
   <si>
+    <t>24,1</t>
+  </si>
+  <si>
     <t>gameover</t>
   </si>
   <si>
     <t>风起</t>
   </si>
   <si>
+    <t>生活压力变大了，在26岁前攒到20000模拟币</t>
+  </si>
+  <si>
     <t>mission:100</t>
   </si>
   <si>
     <t>1012,1</t>
   </si>
   <si>
+    <t>26,1</t>
+  </si>
+  <si>
+    <t>初来乍到</t>
+  </si>
+  <si>
+    <t>初来社区，到处转转，没事做就进入下一回合吧</t>
+  </si>
+  <si>
+    <t>AdvanceTurn</t>
+  </si>
+  <si>
+    <t>force:22,1</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>代购</t>
+  </si>
+  <si>
+    <t>熊大山工具带得很齐，却唯独忘记了最普通的强力胶带</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>force:22,4</t>
+  </si>
+  <si>
+    <t>5102,1</t>
+  </si>
+  <si>
+    <t>collect</t>
+  </si>
+  <si>
+    <t>MissionRole,0</t>
+  </si>
+  <si>
+    <t>MissionRole,1</t>
+  </si>
+  <si>
+    <t>社区报到</t>
+  </si>
+  <si>
+    <t>进入社区</t>
+  </si>
+  <si>
+    <t>CommunityCentreView</t>
+  </si>
+  <si>
+    <t>force:22,2</t>
+  </si>
+  <si>
+    <t>MissionRole,3</t>
+  </si>
+  <si>
+    <t>问诊</t>
+  </si>
+  <si>
+    <t>进入医务室</t>
+  </si>
+  <si>
+    <t>ClinicView</t>
+  </si>
+  <si>
+    <t>force:22,3</t>
+  </si>
+  <si>
+    <t>MissionRole,5</t>
+  </si>
+  <si>
+    <t>外出捕食</t>
+  </si>
+  <si>
     <t>完成一次零工</t>
   </si>
   <si>
+    <t>Work</t>
+  </si>
+  <si>
     <t>101,500</t>
   </si>
   <si>
+    <t>MissionOne,0</t>
+  </si>
+  <si>
     <t>MissionOne,1</t>
   </si>
   <si>
@@ -211,9 +301,6 @@
     <t>mission:1002</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>生病啦</t>
   </si>
   <si>
@@ -247,9 +334,6 @@
     <t>社区发布需求，需要提交&lt;color=#00FFFA&gt;{0}&lt;/color&gt;*{1}</t>
   </si>
   <si>
-    <t>Item</t>
-  </si>
-  <si>
     <t>submit</t>
   </si>
   <si>
@@ -271,9 +355,6 @@
     <t>5101,1</t>
   </si>
   <si>
-    <t>collect</t>
-  </si>
-  <si>
     <t>3001,1;4023,3</t>
   </si>
   <si>
@@ -304,6 +385,9 @@
     <t>社区鱼获需求</t>
   </si>
   <si>
+    <t>请亲自钓起以下鱼获，已有鱼获不计：{0}*{1}</t>
+  </si>
+  <si>
     <t>FishCatch</t>
   </si>
   <si>
@@ -314,60 +398,6 @@
   </si>
   <si>
     <t>6000,3,10;6001,3,10;6002,3,10;6003,2,10;6004,2,10;6005,2,10;6006,1,10;6007,1,10;6008,1,10;6009,1,10;6010,1,10</t>
-  </si>
-  <si>
-    <t>请亲自钓起以下鱼获，已有鱼获不计：{0}*{1}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>在24岁前积累5000模拟币，然后去看看外边的世界吧</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>生活压力变大了，在26岁前攒到20000模拟币</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>24,1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>26,1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>熊大山工具带得很齐，却唯独忘记了最普通的强力胶带</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>5102,1</t>
-  </si>
-  <si>
-    <t>MissionRole,0</t>
-  </si>
-  <si>
-    <t>外出捕食</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MissionOne,0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Work</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>force:22,4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>代购</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MissionRole,1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -393,7 +423,6 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -420,7 +449,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -432,9 +461,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -710,26 +736,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="16" style="2" customWidth="1"/>
-    <col min="4" max="4" width="60.21875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="23.21875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.44140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.33203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="60.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="23.375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="20.25" style="2" customWidth="1"/>
     <col min="14" max="14" width="20" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.6640625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="24.625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -776,7 +802,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -823,7 +849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -870,7 +896,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -917,7 +943,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>100</v>
       </c>
@@ -925,458 +951,513 @@
         <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>1002</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="M5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N5"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>101</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>1002</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H6">
         <v>20000</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B7">
         <v>102</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B7">
-        <v>200</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="F7">
-        <v>5012</v>
+        <v>3011</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>109</v>
+        <v>50</v>
       </c>
       <c r="H7" t="s">
-        <v>104</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-      <c r="N7" t="s">
-        <v>105</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N7"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B8">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F8" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G8" s="1"/>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>44</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8">
+        <v>5102</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
-      <c r="N8" s="1" t="s">
-        <v>107</v>
+      <c r="N8" t="s">
+        <v>58</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B9">
-        <v>1001</v>
+        <v>201</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1010</v>
+        <v>61</v>
+      </c>
+      <c r="E9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9">
+        <v>3011</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>50</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="H9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
-      <c r="N9" s="1" t="s">
+      <c r="N9" t="s">
+        <v>64</v>
+      </c>
+      <c r="O9" s="1"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B10">
+        <v>202</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10">
+        <v>1050</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" t="s">
         <v>51</v>
       </c>
-      <c r="O9" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B10">
-        <v>1002</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10">
-        <v>2000</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
-      <c r="N10" s="1" t="s">
+      <c r="N10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B11">
+        <v>1000</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="1">
+        <v>4000</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>1001</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1010</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>1002</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13">
+        <v>2000</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>1003</v>
+      </c>
+      <c r="C14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14">
+        <v>2000</v>
+      </c>
+      <c r="G14" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" t="s">
+        <v>51</v>
+      </c>
+      <c r="K14" t="s">
+        <v>73</v>
+      </c>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>2000</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1050</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15">
+        <v>80</v>
+      </c>
+      <c r="L15">
+        <v>6</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>3000</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1011</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L16"/>
+      <c r="M16" s="1"/>
+      <c r="N16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <v>3001</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17">
+        <v>3011</v>
+      </c>
+      <c r="I17" t="s">
+        <v>104</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <v>3002</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="1">
+        <v>5101</v>
+      </c>
+      <c r="G18" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" t="s">
+        <v>110</v>
+      </c>
+      <c r="I18" t="s">
         <v>57</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11">
-        <v>1003</v>
-      </c>
-      <c r="C11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11">
-        <v>2000</v>
-      </c>
-      <c r="G11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H11" t="s">
-        <v>63</v>
-      </c>
-      <c r="K11" t="s">
-        <v>44</v>
-      </c>
-      <c r="L11"/>
-      <c r="M11"/>
-      <c r="N11"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B12">
-        <v>2000</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1050</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H12">
-        <v>80</v>
-      </c>
-      <c r="L12">
-        <v>6</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B13">
-        <v>3000</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1011</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H13" t="s">
-        <v>63</v>
-      </c>
-      <c r="L13"/>
-      <c r="M13" s="1"/>
-      <c r="N13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B14">
-        <v>3001</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F14">
-        <v>3011</v>
-      </c>
-      <c r="I14" t="s">
-        <v>76</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B15">
-        <v>3002</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="1">
-        <v>5101</v>
-      </c>
-      <c r="G15" t="s">
-        <v>81</v>
-      </c>
-      <c r="H15" t="s">
-        <v>82</v>
-      </c>
-      <c r="I15" t="s">
-        <v>83</v>
-      </c>
-      <c r="K15" t="s">
-        <v>84</v>
-      </c>
-      <c r="L15"/>
-      <c r="M15"/>
-      <c r="N15" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B16">
-        <v>3003</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="1">
-        <v>5100</v>
-      </c>
-      <c r="G16" t="s">
-        <v>89</v>
-      </c>
-      <c r="H16" t="s">
-        <v>90</v>
-      </c>
-      <c r="I16" t="s">
-        <v>83</v>
-      </c>
-      <c r="K16" t="s">
-        <v>84</v>
-      </c>
-      <c r="L16"/>
-      <c r="M16"/>
-      <c r="N16" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <v>3004</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17">
-        <v>6000</v>
-      </c>
-      <c r="G17" t="s">
-        <v>95</v>
-      </c>
-      <c r="H17" t="s">
-        <v>96</v>
-      </c>
-      <c r="I17" t="s">
-        <v>83</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="L17"/>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B18"/>
-      <c r="C18"/>
-      <c r="D18"/>
-      <c r="E18"/>
-      <c r="F18" s="1"/>
-      <c r="G18"/>
-      <c r="H18"/>
-      <c r="K18"/>
+      <c r="K18" t="s">
+        <v>111</v>
+      </c>
       <c r="L18"/>
       <c r="M18"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="F19" s="1"/>
-      <c r="G19"/>
-      <c r="H19"/>
-      <c r="K19"/>
+      <c r="N18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <v>3003</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5100</v>
+      </c>
+      <c r="G19" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19" t="s">
+        <v>117</v>
+      </c>
+      <c r="I19" t="s">
+        <v>57</v>
+      </c>
+      <c r="K19" t="s">
+        <v>111</v>
+      </c>
       <c r="L19"/>
       <c r="M19"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20" s="1"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="K20"/>
+      <c r="N19" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>3004</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20">
+        <v>6000</v>
+      </c>
+      <c r="G20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H20" t="s">
+        <v>124</v>
+      </c>
+      <c r="I20" t="s">
+        <v>57</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>111</v>
+      </c>
       <c r="L20"/>
-      <c r="M20"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1388,7 +1469,7 @@
       <c r="L21"/>
       <c r="M21"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -1400,20 +1481,56 @@
       <c r="L22"/>
       <c r="M22"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
       <c r="F23" s="1"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
       <c r="F24" s="1"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
       <c r="F25" s="1"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="F30" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F8C1DD-8DFA-4151-A014-3F54898B52D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7283755-A3DC-4746-B845-5E0ECD18731D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="136">
   <si>
     <t>##var</t>
   </si>
@@ -127,6 +127,9 @@
     <t>第一桶金</t>
   </si>
   <si>
+    <t>在24岁前积累模拟币，然后去看看外边的世界吧</t>
+  </si>
+  <si>
     <t>SimulationCoinBalance</t>
   </si>
   <si>
@@ -178,6 +181,9 @@
     <t>代购</t>
   </si>
   <si>
+    <t>熊大山工具带得很齐，却唯独忘记了胶带</t>
+  </si>
+  <si>
     <t>Item</t>
   </si>
   <si>
@@ -199,6 +205,9 @@
     <t>社区报到</t>
   </si>
   <si>
+    <t>进入沿江社区中心</t>
+  </si>
+  <si>
     <t>CommunityCentreView</t>
   </si>
   <si>
@@ -211,6 +220,9 @@
     <t>问诊</t>
   </si>
   <si>
+    <t>进入沿江医务室</t>
+  </si>
+  <si>
     <t>ClinicView</t>
   </si>
   <si>
@@ -400,19 +412,22 @@
     <t>MissionThree,5</t>
   </si>
   <si>
-    <t>进入沿江社区中心</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>进入沿江医务室</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>熊大山工具带得很齐，却唯独忘记了胶带</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>在24岁前积累模拟币，然后去看看外边的世界吧</t>
+    <t>端午促销</t>
+  </si>
+  <si>
+    <t>ConvenienceStorePurchase</t>
+  </si>
+  <si>
+    <t>5200,3;5201,3;5202,3;5203,10</t>
+  </si>
+  <si>
+    <t>Festival,0</t>
+  </si>
+  <si>
+    <t>Festival,1</t>
+  </si>
+  <si>
+    <t>端午时节，进入便利店购买任意一件商品</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -439,7 +454,6 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -754,25 +768,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="16" style="2" customWidth="1"/>
-    <col min="4" max="4" width="60.21875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="23.21875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.44140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.33203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="60.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="23.375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="20.25" style="2" customWidth="1"/>
     <col min="14" max="14" width="20" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.6640625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="24.625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -819,7 +833,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -866,7 +880,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -913,7 +927,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -960,7 +974,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>100</v>
       </c>
@@ -968,147 +982,147 @@
         <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>129</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>1002</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N5"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>101</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>1002</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H6">
         <v>20000</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N6"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>102</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7">
         <v>3011</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>200</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F8">
         <v>5102</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>201</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F9">
         <v>3011</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1116,31 +1130,31 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>202</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>127</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F10">
         <v>1050</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1148,22 +1162,22 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>1000</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F11" s="1">
         <v>4000</v>
@@ -1173,132 +1187,132 @@
         <v>1</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>1001</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F12" s="1">
         <v>1010</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>1002</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F13">
         <v>2000</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>1003</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F14">
         <v>2000</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L14"/>
       <c r="M14"/>
       <c r="N14"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>2000</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F15" s="1">
         <v>1050</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H15">
         <v>80</v>
@@ -1307,220 +1321,242 @@
         <v>6</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>3000</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F16" s="1">
         <v>1011</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L16"/>
       <c r="M16" s="1"/>
       <c r="N16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>3001</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F17">
         <v>3011</v>
       </c>
       <c r="I17" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="L17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>3002</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F18" s="1">
         <v>5101</v>
       </c>
       <c r="G18" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H18" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K18" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L18"/>
       <c r="M18"/>
       <c r="N18" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>3003</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F19" s="1">
         <v>5100</v>
       </c>
       <c r="G19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H19" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L19"/>
       <c r="M19"/>
       <c r="N19" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>3004</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F20">
         <v>6000</v>
       </c>
       <c r="G20" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H20" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L20"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>3005</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F21" s="1">
         <v>3011</v>
       </c>
       <c r="G21"/>
       <c r="H21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M21"/>
       <c r="N21" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O21"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22"/>
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22" s="1"/>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>4000</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="1">
+        <v>3100</v>
+      </c>
       <c r="G22"/>
-      <c r="H22"/>
-      <c r="K22"/>
+      <c r="H22" t="s">
+        <v>51</v>
+      </c>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22" t="s">
+        <v>132</v>
+      </c>
       <c r="L22"/>
       <c r="M22"/>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="N22" t="s">
+        <v>133</v>
+      </c>
+      <c r="O22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -1532,7 +1568,7 @@
       <c r="L23"/>
       <c r="M23"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
@@ -1544,7 +1580,7 @@
       <c r="L24"/>
       <c r="M24"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -1556,19 +1592,19 @@
       <c r="L25"/>
       <c r="M25"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F30" s="1"/>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7283755-A3DC-4746-B845-5E0ECD18731D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB5CEE4-65A6-4985-8F71-CCC38F763246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="141">
   <si>
     <t>##var</t>
   </si>
@@ -241,193 +241,212 @@
     <t>Work</t>
   </si>
   <si>
+    <t>MissionOne,0</t>
+  </si>
+  <si>
+    <t>MissionOne,1</t>
+  </si>
+  <si>
+    <t>从天而降的好运</t>
+  </si>
+  <si>
+    <t>前往系统空间，使用&lt;color=#00FFFA&gt;时间币&lt;/color&gt;进行一次抽奖</t>
+  </si>
+  <si>
+    <t>NormalLottery</t>
+  </si>
+  <si>
+    <t>mission:1000</t>
+  </si>
+  <si>
+    <t>101,500;102,1</t>
+  </si>
+  <si>
+    <t>MissionOne,2</t>
+  </si>
+  <si>
+    <t>MissionOne,3</t>
+  </si>
+  <si>
+    <t>添置家具</t>
+  </si>
+  <si>
+    <t>购买任意家具</t>
+  </si>
+  <si>
+    <t>HomePurchaseAny</t>
+  </si>
+  <si>
+    <t>mission:1001</t>
+  </si>
+  <si>
+    <t>MissionOne,4</t>
+  </si>
+  <si>
+    <t>MissionOne,5</t>
+  </si>
+  <si>
+    <t>温馨小屋</t>
+  </si>
+  <si>
+    <t>查看小屋满意度面板</t>
+  </si>
+  <si>
+    <t>HomeSatisfactionView</t>
+  </si>
+  <si>
+    <t>mission:1002</t>
+  </si>
+  <si>
+    <t>生病啦</t>
+  </si>
+  <si>
+    <t>你的基础生命过低</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>healthBelow:40</t>
+  </si>
+  <si>
+    <t>神秘转盘！</t>
+  </si>
+  <si>
+    <t>获得了一枚&lt;color=#00FFFA&gt;转盘币&lt;/color&gt;，使用其进行一次抽奖</t>
+  </si>
+  <si>
+    <t>MysteryWheelLottery</t>
+  </si>
+  <si>
+    <t>wheelCoinObtained</t>
+  </si>
+  <si>
+    <t>MissionThree,0</t>
+  </si>
+  <si>
+    <t>社区物资需求</t>
+  </si>
+  <si>
+    <t>社区发布需求，需要提交&lt;color=#00FFFA&gt;{0}&lt;/color&gt;*{1}</t>
+  </si>
+  <si>
+    <t>submit</t>
+  </si>
+  <si>
+    <t>5000,3,10;5001,3,10;5002,3,10;5003,3,10;5004,3,10;5005,3,10</t>
+  </si>
+  <si>
+    <t>3011,1</t>
+  </si>
+  <si>
+    <t>海洋之心</t>
+  </si>
+  <si>
+    <t>收集&lt;color=#00FFFA&gt;{0}&lt;/color&gt;×{1}，送给喵夫人</t>
+  </si>
+  <si>
+    <t>satisfactionAtLeast:40</t>
+  </si>
+  <si>
+    <t>5101,1</t>
+  </si>
+  <si>
+    <t>MissionThree,3</t>
+  </si>
+  <si>
+    <t>MissionThree,4</t>
+  </si>
+  <si>
+    <t>草莓小熊</t>
+  </si>
+  <si>
+    <t>女儿的心愿，收集&lt;color=#00FFFA&gt;{0}&lt;/color&gt;×{1}</t>
+  </si>
+  <si>
+    <t>unlockedHomeIdRangeCount:7000,7999,3</t>
+  </si>
+  <si>
+    <t>5100,1</t>
+  </si>
+  <si>
+    <t>MissionThree,1</t>
+  </si>
+  <si>
+    <t>MissionThree,2</t>
+  </si>
+  <si>
+    <t>社区鱼获需求</t>
+  </si>
+  <si>
+    <t>请亲自钓起以下鱼获，已有鱼获不计：{0}*{1}</t>
+  </si>
+  <si>
+    <t>FishCatch</t>
+  </si>
+  <si>
+    <t>mission:3003</t>
+  </si>
+  <si>
+    <t>6000,3;6001,3;6002,3;6003,2;6004,2;6005,2;6006,1;6007,1;6008,1;6009,1;6010,1</t>
+  </si>
+  <si>
+    <t>6000,3,10;6001,3,10;6002,3,10;6003,2,10;6004,2,10;6005,2,10;6006,1,10;6007,1,10;6008,1,10;6009,1,10;6010,1,10</t>
+  </si>
+  <si>
+    <t>鹿伯安的委托</t>
+  </si>
+  <si>
+    <t>帮鹿伯安完成文件盖章挑战</t>
+  </si>
+  <si>
+    <t>GameStamp</t>
+  </si>
+  <si>
+    <t>MissionThree,5</t>
+  </si>
+  <si>
+    <t>端午促销</t>
+  </si>
+  <si>
+    <t>ConvenienceStorePurchase</t>
+  </si>
+  <si>
+    <t>5200,3;5201,3;5202,3;5203,10</t>
+  </si>
+  <si>
+    <t>Festival,0</t>
+  </si>
+  <si>
+    <t>Festival,1</t>
+  </si>
+  <si>
+    <t>端午时节，进入便利店购买任意一件商品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>settlementMemoryPoint</t>
+  </si>
+  <si>
+    <t>娓告垙缁撶畻鍙幏寰楃殑鍥炲繂鐐规暟</t>
+  </si>
+  <si>
+    <t>MissionMain,0</t>
+  </si>
+  <si>
     <t>101,500</t>
-  </si>
-  <si>
-    <t>MissionOne,0</t>
-  </si>
-  <si>
-    <t>MissionOne,1</t>
-  </si>
-  <si>
-    <t>从天而降的好运</t>
-  </si>
-  <si>
-    <t>前往系统空间，使用&lt;color=#00FFFA&gt;时间币&lt;/color&gt;进行一次抽奖</t>
-  </si>
-  <si>
-    <t>NormalLottery</t>
-  </si>
-  <si>
-    <t>mission:1000</t>
-  </si>
-  <si>
-    <t>101,500;102,1</t>
-  </si>
-  <si>
-    <t>MissionOne,2</t>
-  </si>
-  <si>
-    <t>MissionOne,3</t>
-  </si>
-  <si>
-    <t>添置家具</t>
-  </si>
-  <si>
-    <t>购买任意家具</t>
-  </si>
-  <si>
-    <t>HomePurchaseAny</t>
-  </si>
-  <si>
-    <t>mission:1001</t>
-  </si>
-  <si>
-    <t>MissionOne,4</t>
-  </si>
-  <si>
-    <t>MissionOne,5</t>
-  </si>
-  <si>
-    <t>温馨小屋</t>
-  </si>
-  <si>
-    <t>查看小屋满意度面板</t>
-  </si>
-  <si>
-    <t>HomeSatisfactionView</t>
-  </si>
-  <si>
-    <t>mission:1002</t>
-  </si>
-  <si>
-    <t>生病啦</t>
-  </si>
-  <si>
-    <t>你的基础生命过低</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>healthBelow:40</t>
-  </si>
-  <si>
-    <t>神秘转盘！</t>
-  </si>
-  <si>
-    <t>获得了一枚&lt;color=#00FFFA&gt;转盘币&lt;/color&gt;，使用其进行一次抽奖</t>
-  </si>
-  <si>
-    <t>MysteryWheelLottery</t>
-  </si>
-  <si>
-    <t>wheelCoinObtained</t>
-  </si>
-  <si>
-    <t>MissionThree,0</t>
-  </si>
-  <si>
-    <t>社区物资需求</t>
-  </si>
-  <si>
-    <t>社区发布需求，需要提交&lt;color=#00FFFA&gt;{0}&lt;/color&gt;*{1}</t>
-  </si>
-  <si>
-    <t>submit</t>
-  </si>
-  <si>
-    <t>5000,3,10;5001,3,10;5002,3,10;5003,3,10;5004,3,10;5005,3,10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3011,1;101,100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>3011,1</t>
-  </si>
-  <si>
-    <t>海洋之心</t>
-  </si>
-  <si>
-    <t>收集&lt;color=#00FFFA&gt;{0}&lt;/color&gt;×{1}，送给喵夫人</t>
-  </si>
-  <si>
-    <t>satisfactionAtLeast:40</t>
-  </si>
-  <si>
-    <t>5101,1</t>
-  </si>
-  <si>
-    <t>3001,1;4023,3</t>
-  </si>
-  <si>
-    <t>MissionThree,3</t>
-  </si>
-  <si>
-    <t>MissionThree,4</t>
-  </si>
-  <si>
-    <t>草莓小熊</t>
-  </si>
-  <si>
-    <t>女儿的心愿，收集&lt;color=#00FFFA&gt;{0}&lt;/color&gt;×{1}</t>
-  </si>
-  <si>
-    <t>unlockedHomeIdRangeCount:7000,7999,3</t>
-  </si>
-  <si>
-    <t>5100,1</t>
-  </si>
-  <si>
-    <t>MissionThree,1</t>
-  </si>
-  <si>
-    <t>MissionThree,2</t>
-  </si>
-  <si>
-    <t>社区鱼获需求</t>
-  </si>
-  <si>
-    <t>请亲自钓起以下鱼获，已有鱼获不计：{0}*{1}</t>
-  </si>
-  <si>
-    <t>FishCatch</t>
-  </si>
-  <si>
-    <t>mission:3003</t>
-  </si>
-  <si>
-    <t>6000,3;6001,3;6002,3;6003,2;6004,2;6005,2;6006,1;6007,1;6008,1;6009,1;6010,1</t>
-  </si>
-  <si>
-    <t>6000,3,10;6001,3,10;6002,3,10;6003,2,10;6004,2,10;6005,2,10;6006,1,10;6007,1,10;6008,1,10;6009,1,10;6010,1,10</t>
-  </si>
-  <si>
-    <t>鹿伯安的委托</t>
-  </si>
-  <si>
-    <t>帮鹿伯安完成文件盖章挑战</t>
-  </si>
-  <si>
-    <t>GameStamp</t>
-  </si>
-  <si>
-    <t>MissionThree,5</t>
-  </si>
-  <si>
-    <t>端午促销</t>
-  </si>
-  <si>
-    <t>ConvenienceStorePurchase</t>
-  </si>
-  <si>
-    <t>5200,3;5201,3;5202,3;5203,10</t>
-  </si>
-  <si>
-    <t>Festival,0</t>
-  </si>
-  <si>
-    <t>Festival,1</t>
-  </si>
-  <si>
-    <t>端午时节，进入便利店购买任意一件商品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3012,1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -480,7 +499,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -492,6 +511,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -767,26 +793,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:P30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="16" style="2" customWidth="1"/>
-    <col min="4" max="4" width="60.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="23.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="20.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="60.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.21875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.44140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="23.33203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="20.21875" style="2" customWidth="1"/>
     <col min="14" max="14" width="20" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="24.6640625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -832,8 +859,11 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -879,8 +909,11 @@
       <c r="O2" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -926,8 +959,11 @@
       <c r="O3" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -973,8 +1009,11 @@
       <c r="O4" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>100</v>
       </c>
@@ -1006,8 +1045,14 @@
         <v>41</v>
       </c>
       <c r="N5"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O5" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>101</v>
       </c>
@@ -1039,8 +1084,11 @@
         <v>41</v>
       </c>
       <c r="N6"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>102</v>
       </c>
@@ -1062,12 +1110,17 @@
       <c r="H7" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="1"/>
+      <c r="K7" s="5">
+        <v>101100</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>200</v>
       </c>
@@ -1092,7 +1145,9 @@
       <c r="I8" t="s">
         <v>57</v>
       </c>
-      <c r="K8" s="1"/>
+      <c r="K8" s="5">
+        <v>101100</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" t="s">
@@ -1101,8 +1156,11 @@
       <c r="O8" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>201</v>
       </c>
@@ -1126,15 +1184,20 @@
       </c>
       <c r="I9"/>
       <c r="J9"/>
-      <c r="K9" s="1"/>
+      <c r="K9" s="5">
+        <v>101100</v>
+      </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" t="s">
         <v>64</v>
       </c>
       <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>202</v>
       </c>
@@ -1158,15 +1221,20 @@
       </c>
       <c r="I10"/>
       <c r="J10"/>
-      <c r="K10" s="1"/>
+      <c r="K10" s="5">
+        <v>101100</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" t="s">
         <v>69</v>
       </c>
       <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1000</v>
       </c>
@@ -1187,132 +1255,144 @@
         <v>1</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="O11" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>1001</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="F12" s="1">
         <v>1010</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="O12" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>1002</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="F13">
         <v>2000</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>73</v>
+      <c r="K13" s="5">
+        <v>101200</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="O13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>1003</v>
       </c>
       <c r="C14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" t="s">
         <v>89</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>90</v>
-      </c>
-      <c r="E14" t="s">
-        <v>91</v>
       </c>
       <c r="F14">
         <v>2000</v>
       </c>
       <c r="G14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s">
         <v>51</v>
       </c>
-      <c r="K14" t="s">
-        <v>73</v>
+      <c r="K14" s="6">
+        <v>101200</v>
       </c>
       <c r="L14"/>
       <c r="M14"/>
       <c r="N14"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>2000</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="F15" s="1">
         <v>1050</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H15">
         <v>80</v>
@@ -1323,44 +1403,53 @@
       <c r="M15" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>3000</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="F16" s="1">
         <v>1011</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H16" t="s">
         <v>51</v>
+      </c>
+      <c r="K16" s="7">
+        <v>101100</v>
       </c>
       <c r="L16"/>
       <c r="M16" s="1"/>
       <c r="N16" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>3001</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>54</v>
@@ -1369,27 +1458,30 @@
         <v>3011</v>
       </c>
       <c r="I17" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="L17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>3002</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>54</v>
@@ -1398,35 +1490,38 @@
         <v>5101</v>
       </c>
       <c r="G18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H18" t="s">
         <v>109</v>
-      </c>
-      <c r="H18" t="s">
-        <v>110</v>
       </c>
       <c r="I18" t="s">
         <v>57</v>
       </c>
-      <c r="K18" t="s">
-        <v>111</v>
+      <c r="K18" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="L18"/>
       <c r="M18"/>
       <c r="N18" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>3003</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>54</v>
@@ -1435,71 +1530,79 @@
         <v>5100</v>
       </c>
       <c r="G19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H19" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I19" t="s">
         <v>57</v>
       </c>
-      <c r="K19" t="s">
-        <v>111</v>
+      <c r="K19" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="L19"/>
       <c r="M19"/>
       <c r="N19" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>3004</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="F20">
         <v>6000</v>
       </c>
       <c r="G20" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I20" t="s">
         <v>57</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="L20"/>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>3005</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" t="s">
         <v>126</v>
-      </c>
-      <c r="D21" t="s">
-        <v>127</v>
-      </c>
-      <c r="E21" t="s">
-        <v>128</v>
       </c>
       <c r="F21" s="1">
         <v>3011</v>
@@ -1510,30 +1613,33 @@
       </c>
       <c r="I21"/>
       <c r="J21"/>
-      <c r="K21" t="s">
-        <v>111</v>
+      <c r="K21" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="L21" t="s">
         <v>51</v>
       </c>
       <c r="M21"/>
       <c r="N21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="O21"/>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>4000</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E22" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F22" s="1">
         <v>3100</v>
@@ -1545,18 +1651,21 @@
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L22"/>
       <c r="M22"/>
       <c r="N22" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="O22" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -1568,7 +1677,7 @@
       <c r="L23"/>
       <c r="M23"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
@@ -1580,7 +1689,7 @@
       <c r="L24"/>
       <c r="M24"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -1592,19 +1701,19 @@
       <c r="L25"/>
       <c r="M25"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
       <c r="F30" s="1"/>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB5CEE4-65A6-4985-8F71-CCC38F763246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1D4E3A-4CB1-4275-91BF-0CA9BA3E1EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="143">
   <si>
     <t>##var</t>
   </si>
@@ -431,9 +431,6 @@
     <t>娓告垙缁撶畻鍙幏寰楃殑鍥炲繂鐐规暟</t>
   </si>
   <si>
-    <t>MissionMain,0</t>
-  </si>
-  <si>
     <t>101,500</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -447,6 +444,18 @@
   </si>
   <si>
     <t>3012,1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,200</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissionMain,0</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -499,7 +508,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -511,13 +520,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1044,10 +1047,10 @@
       <c r="M5" t="s">
         <v>41</v>
       </c>
-      <c r="N5"/>
-      <c r="O5" s="1" t="s">
-        <v>136</v>
-      </c>
+      <c r="N5" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="O5" s="1"/>
       <c r="P5">
         <v>10</v>
       </c>
@@ -1110,8 +1113,8 @@
       <c r="H7" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="5">
-        <v>101100</v>
+      <c r="K7" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -1145,8 +1148,8 @@
       <c r="I8" t="s">
         <v>57</v>
       </c>
-      <c r="K8" s="5">
-        <v>101100</v>
+      <c r="K8" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -1184,8 +1187,8 @@
       </c>
       <c r="I9"/>
       <c r="J9"/>
-      <c r="K9" s="5">
-        <v>101100</v>
+      <c r="K9" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -1221,8 +1224,8 @@
       </c>
       <c r="I10"/>
       <c r="J10"/>
-      <c r="K10" s="5">
-        <v>101100</v>
+      <c r="K10" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1255,7 +1258,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -1328,8 +1331,8 @@
       <c r="H13">
         <v>1</v>
       </c>
-      <c r="K13" s="5">
-        <v>101200</v>
+      <c r="K13" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1365,8 +1368,8 @@
       <c r="H14" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="6">
-        <v>101200</v>
+      <c r="K14" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="L14"/>
       <c r="M14"/>
@@ -1429,8 +1432,8 @@
       <c r="H16" t="s">
         <v>51</v>
       </c>
-      <c r="K16" s="7">
-        <v>101100</v>
+      <c r="K16" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="L16"/>
       <c r="M16" s="1"/>
@@ -1499,7 +1502,7 @@
         <v>57</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L18"/>
       <c r="M18"/>
@@ -1539,7 +1542,7 @@
         <v>57</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L19"/>
       <c r="M19"/>
@@ -1582,7 +1585,7 @@
         <v>123</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L20">
         <v>2</v>
@@ -1614,7 +1617,7 @@
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L21" t="s">
         <v>51</v>
